--- a/00-TrainRnns/tau-12/Theta/BestModels-otm.xlsx
+++ b/00-TrainRnns/tau-12/Theta/BestModels-otm.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,222 +557,6 @@
       </c>
       <c r="P2" t="n">
         <v>0.9828176905267212</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>4742</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>model_arch49-24_r0.9_Ld0.7_Lp0.3_seed5928</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[49, 24]</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.9817680847658076</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.1992274506162217</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.614009361458552</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0.4858068751334346</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-24.40373930372658</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-2.578539890970043</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-1.227957925273408</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.3138784168076618</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-55.77955177153709</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.9817680847658076</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-0.1992274506162217</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-11.93538685548205</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.9817680847658076</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>5370</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>model_arch54-27_r0.9_Ld0.7_Lp0.3_seed1716</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[54, 27]</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.980438559044653</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7710501193500729</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.7436414821844388</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.3874697081907618</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-18.09037153539486</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-5.314752269115354</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-1.858510934086499</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.886204740219269</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-47.43690911578414</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.980438559044653</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.7710501193500729</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-10.3508053434607</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.980438559044653</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>1077</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>model_arch36_r0.9_Ld0.7_Lp0.3_seed7320</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[36]</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.980072658916902</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.6464798634856744</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.911628143047471</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.3347015781858158</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-23.98646326453994</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-9.221765854729018</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-2.438578078134813</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-1.319799884913706</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-56.04470394573162</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.980072658916902</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.6464798634856744</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-13.20491206616963</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.980072658916902</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>5579</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>model_arch54-34_r0.01_Ld0.7_Lp0.3_seed5071</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[54, 34]</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.9774865428544629</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.5447463383281654</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.8760279551939495</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.3975474053330581</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-22.60662773290696</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-10.40616711968311</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-3.963441042014369</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.3380202954093401</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-58.20319790278147</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.9774865428544629</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.5447463383281654</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-13.57699622041919</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.9774865428544629</v>
       </c>
     </row>
   </sheetData>
